--- a/docs/timelog/limajr28/Joshua Lima - Timelogs.xlsx
+++ b/docs/timelog/limajr28/Joshua Lima - Timelogs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Date</t>
   </si>
@@ -248,6 +248,21 @@
       </rPr>
       <t>: Went over last week's progress and assigned work for the upcoming week.</t>
     </r>
+  </si>
+  <si>
+    <t>Cleaned up processing code to make it more readable, as well as adding in proper documentation to the code.</t>
+  </si>
+  <si>
+    <t>Added image processing information to the design document.</t>
+  </si>
+  <si>
+    <t>Wrote up most sections for the user manual. Didn't address setting up the database as I have little information on how exactly it is done.</t>
+  </si>
+  <si>
+    <t>Cleaned up the design documentation a bit and added a new section to help clarify some terminology.</t>
+  </si>
+  <si>
+    <t>Revised the presentation and added a new section to it to explain image annotation.</t>
   </si>
 </sst>
 </file>
@@ -802,6 +817,61 @@
         <v>26</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>46127.0</v>
+      </c>
+      <c r="B26" s="3">
+        <v>60.0</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>46128.0</v>
+      </c>
+      <c r="B27" s="3">
+        <v>60.0</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>46130.0</v>
+      </c>
+      <c r="B28" s="3">
+        <v>90.0</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>46131.0</v>
+      </c>
+      <c r="B29" s="3">
+        <v>60.0</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>46135.0</v>
+      </c>
+      <c r="B30" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
